--- a/Exc2/FURPS_table.xlsx
+++ b/Exc2/FURPS_table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\architecture-sprint-9\Exc2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9BF1C2A-A2D5-444A-8082-33EE37EBC866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50E1C3BD-40CC-436E-B752-BB91741C451F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6375" yWindow="7095" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
   <si>
     <t>Код</t>
   </si>
@@ -118,9 +118,6 @@
     <t>Подключение к сайту должно быть защищено протоколом TLS 1.3</t>
   </si>
   <si>
-    <t>Сетевое подключение к интернет-банку дожно быть защищено протоколом TLS 1.3</t>
-  </si>
-  <si>
     <t>В качестве баз данных должны использоваться MS SQL и Oracle</t>
   </si>
   <si>
@@ -151,31 +148,9 @@
     <t>F6</t>
   </si>
   <si>
-    <t>После успешного утверждения создания димозита клиент должен получить СМС-уведомление об открытии депозита</t>
-  </si>
-  <si>
     <t>В интенет-банке клиент должен видеть персонализированные ставки среди доступных для открытия депозитов</t>
   </si>
   <si>
-    <t>В АБС должен быть реализован механизм согласовние ставки по заявке создания дипозита</t>
-  </si>
-  <si>
-    <t>В АБС должен быть реализован учет ставок по дипозитам</t>
-  </si>
-  <si>
-    <t>Обязательными параметрами для создания заявки на открытие дипозита должны быть номер счета и сумма депозита</t>
-  </si>
-  <si>
-    <t>В интернет-банке клиент должен видеть список доступных депозитов с актуальными ставками</t>
-  </si>
-  <si>
-    <t>Клиент подает заявку на депозит, указывая свой номер телефона и Ф. И. О.
-Номер телефона и Ф.И.О. должны быть обязательны для заполнения</t>
-  </si>
-  <si>
-    <t>Клиента должен подтверждать СМС-кодом создание заявки на открытие депозита</t>
-  </si>
-  <si>
     <t>В качестве новых технологий допускается использовать те технологии, которые могут сопровождаться на уровне исходного кода IT-сотрудниками банка</t>
   </si>
   <si>
@@ -200,9 +175,6 @@
     <t>Сервисы и интернет-банк должны быть доступны 99,9%</t>
   </si>
   <si>
-    <t>R6</t>
-  </si>
-  <si>
     <t>В случае сбоя основного ЦОД работа системы должна переключаться на резервный ЦОД</t>
   </si>
   <si>
@@ -216,6 +188,48 @@
   </si>
   <si>
     <t>P3</t>
+  </si>
+  <si>
+    <t>F7</t>
+  </si>
+  <si>
+    <t>Сетевое подключение к интернет-банку должно быть защищено протоколом TLS 1.3</t>
+  </si>
+  <si>
+    <t>F8</t>
+  </si>
+  <si>
+    <t>F9</t>
+  </si>
+  <si>
+    <t>Сайт должен иметь возможность подать заявку на депозит</t>
+  </si>
+  <si>
+    <t>Подача заявки на депозит через сайт должна содержать в качестве параметров номер телефона и Ф. И. О.</t>
+  </si>
+  <si>
+    <t>Интернет-банк должен иметь возможность подать заявку на открытие депозита</t>
+  </si>
+  <si>
+    <t>Интернет-банк должен отображать персонализированный для каждого клиента список доступных депозитов с актуальными ставками</t>
+  </si>
+  <si>
+    <t>Сайт</t>
+  </si>
+  <si>
+    <t>Интернет-банк: обязательными параметрами для создания заявки на открытие дипозита должны быть номер счета и сумма депозита</t>
+  </si>
+  <si>
+    <t>АБС: должны сохраняться ставки по депозитам</t>
+  </si>
+  <si>
+    <t>АБС: должен быть реализован механизм согласовние ставки по заявке создания дипозита</t>
+  </si>
+  <si>
+    <t>АБС: должен отправлять СМС-уведомление клиенту после успешного подтверждения условий открытия депозита</t>
+  </si>
+  <si>
+    <t>Интернет-банк: клиента должен подтверждать создание заявки на открытие депозита с помощью СМС-кода от банка</t>
   </si>
 </sst>
 </file>
@@ -395,20 +409,20 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -638,7 +652,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr defaultColWidth="10.42578125" defaultRowHeight="12.75"/>
   <cols>
     <col min="2" max="2" width="6.85546875" customWidth="1"/>
@@ -663,291 +677,317 @@
       <c r="B4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="11"/>
-    </row>
-    <row r="5" spans="2:4" ht="94.5">
-      <c r="B5" s="2" t="s">
+      <c r="D4" s="14"/>
+    </row>
+    <row r="5" spans="2:4" ht="30" customHeight="1">
+      <c r="B5" s="2"/>
+      <c r="C5" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="D5" s="14"/>
+    </row>
+    <row r="6" spans="2:4" ht="31.5">
+      <c r="B6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="D5" s="3"/>
-    </row>
-    <row r="6" spans="2:4" ht="63">
-      <c r="B6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="C6" s="7" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="D6" s="3"/>
     </row>
     <row r="7" spans="2:4" ht="63">
       <c r="B7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D7" s="3"/>
+    </row>
+    <row r="8" spans="2:4" ht="94.5">
+      <c r="B8" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="D7" s="3"/>
-    </row>
-    <row r="8" spans="2:4" ht="31.5">
-      <c r="B8" s="2" t="s">
-        <v>28</v>
-      </c>
       <c r="C8" s="7" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="D8" s="3"/>
     </row>
     <row r="9" spans="2:4" ht="47.25">
       <c r="B9" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="D9" s="3"/>
     </row>
     <row r="10" spans="2:4" ht="78.75">
       <c r="B10" s="2" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="D10" s="3"/>
     </row>
-    <row r="11" spans="2:4" ht="30" customHeight="1">
+    <row r="11" spans="2:4" ht="63">
       <c r="B11" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" s="11"/>
-    </row>
-    <row r="12" spans="2:4" ht="63">
+        <v>41</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D11" s="3"/>
+    </row>
+    <row r="12" spans="2:4" ht="31.5">
       <c r="B12" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>44</v>
+        <v>56</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>66</v>
       </c>
       <c r="D12" s="3"/>
     </row>
     <row r="13" spans="2:4" ht="47.25">
       <c r="B13" s="2" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="D13" s="3"/>
     </row>
-    <row r="14" spans="2:4" ht="30" customHeight="1">
+    <row r="14" spans="2:4" ht="63">
       <c r="B14" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D14" s="11"/>
-    </row>
-    <row r="15" spans="2:4" ht="47.25">
+        <v>59</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" s="3"/>
+    </row>
+    <row r="15" spans="2:4" ht="30" customHeight="1">
       <c r="B15" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D15" s="3"/>
-    </row>
-    <row r="16" spans="2:4" ht="47.25">
+        <v>5</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="14"/>
+    </row>
+    <row r="16" spans="2:4" ht="63">
       <c r="B16" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>50</v>
+        <v>17</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>42</v>
       </c>
       <c r="D16" s="3"/>
     </row>
     <row r="17" spans="1:4" ht="47.25">
       <c r="B17" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D17" s="3"/>
+    </row>
+    <row r="18" spans="1:4" ht="30" customHeight="1">
+      <c r="B18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="14"/>
+    </row>
+    <row r="19" spans="1:4" ht="47.25">
+      <c r="B19" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D19" s="3"/>
+    </row>
+    <row r="20" spans="1:4" ht="47.25">
+      <c r="B20" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D20" s="3"/>
+    </row>
+    <row r="21" spans="1:4" ht="31.5">
+      <c r="B21" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C17" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D17" s="3"/>
-    </row>
-    <row r="18" spans="1:4" ht="31.5">
-      <c r="B18" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="D18" s="3"/>
-    </row>
-    <row r="19" spans="1:4" ht="31.5">
-      <c r="B19" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="D19" s="13"/>
-    </row>
-    <row r="20" spans="1:4" ht="63">
-      <c r="B20" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="D20" s="13"/>
-    </row>
-    <row r="21" spans="1:4" ht="30" customHeight="1">
-      <c r="B21" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="D21" s="11"/>
-    </row>
-    <row r="22" spans="1:4" ht="47.25">
+      <c r="C21" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D21" s="3"/>
+    </row>
+    <row r="22" spans="1:4" ht="31.5">
       <c r="B22" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="D22" s="3"/>
+        <v>46</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D22" s="11"/>
     </row>
     <row r="23" spans="1:4" ht="63">
       <c r="B23" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D23" s="11"/>
+    </row>
+    <row r="24" spans="1:4" ht="30" customHeight="1">
+      <c r="B24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D24" s="14"/>
+    </row>
+    <row r="25" spans="1:4" ht="47.25">
+      <c r="B25" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="D25" s="3"/>
+    </row>
+    <row r="26" spans="1:4" ht="63">
+      <c r="B26" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C23" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="D23" s="3"/>
-    </row>
-    <row r="24" spans="1:4" ht="63">
-      <c r="B24" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D24" s="14"/>
-    </row>
-    <row r="25" spans="1:4" ht="30" customHeight="1">
-      <c r="B25" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D25" s="11"/>
-    </row>
-    <row r="26" spans="1:4" ht="30" customHeight="1">
-      <c r="B26" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>56</v>
+      <c r="C26" s="7" t="s">
+        <v>52</v>
       </c>
       <c r="D26" s="3"/>
     </row>
-    <row r="27" spans="1:4" ht="47.25">
+    <row r="27" spans="1:4" ht="63">
       <c r="B27" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="D27" s="3"/>
+        <v>53</v>
+      </c>
+      <c r="D27" s="12"/>
     </row>
     <row r="28" spans="1:4" ht="30" customHeight="1">
       <c r="B28" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="D28" s="14"/>
+    </row>
+    <row r="29" spans="1:4" ht="30" customHeight="1">
+      <c r="B29" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D29" s="3"/>
+    </row>
+    <row r="30" spans="1:4" ht="47.25">
+      <c r="B30" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D30" s="3"/>
+    </row>
+    <row r="31" spans="1:4" ht="30" customHeight="1">
+      <c r="B31" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C31" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="D28" s="11"/>
-    </row>
-    <row r="29" spans="1:4" ht="35.25" customHeight="1">
-      <c r="A29" s="5"/>
-      <c r="B29" s="6" t="s">
+      <c r="D31" s="14"/>
+    </row>
+    <row r="32" spans="1:4" ht="35.25" customHeight="1">
+      <c r="A32" s="5"/>
+      <c r="B32" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="C32" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D32" s="3"/>
+    </row>
+    <row r="33" spans="1:4" ht="63">
+      <c r="A33" s="5"/>
+      <c r="B33" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C33" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D29" s="3"/>
-    </row>
-    <row r="30" spans="1:4" ht="63">
-      <c r="A30" s="5"/>
-      <c r="B30" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C30" s="7" t="s">
+      <c r="D33" s="3"/>
+    </row>
+    <row r="34" spans="1:4" ht="94.5">
+      <c r="B34" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D30" s="3"/>
-    </row>
-    <row r="31" spans="1:4" ht="94.5">
-      <c r="B31" s="6" t="s">
+      <c r="C34" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D34" s="3"/>
+    </row>
+    <row r="35" spans="1:4" ht="31.5">
+      <c r="B35" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C31" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="D31" s="3"/>
-    </row>
-    <row r="32" spans="1:4" ht="31.5">
-      <c r="B32" s="6" t="s">
+      <c r="C35" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D35" s="3"/>
+    </row>
+    <row r="36" spans="1:4" ht="94.5">
+      <c r="B36" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="C36" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D32" s="3"/>
-    </row>
-    <row r="33" spans="2:4" ht="94.5">
-      <c r="B33" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C33" s="7" t="s">
+      <c r="D36" s="3"/>
+    </row>
+    <row r="37" spans="1:4" ht="63">
+      <c r="B37" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D33" s="3"/>
-    </row>
-    <row r="34" spans="2:4" ht="63">
-      <c r="B34" s="6" t="s">
+      <c r="C37" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C34" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D34" s="9"/>
+      <c r="D37" s="9"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C24:D24"/>
     <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C5:D5"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51181102362204689" footer="0.51181102362204689"/>

--- a/Exc2/FURPS_table.xlsx
+++ b/Exc2/FURPS_table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\architecture-sprint-9\Exc2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50E1C3BD-40CC-436E-B752-BB91741C451F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB862E9B-A5EA-4C0C-8A66-F2AC6C1D6587}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6375" yWindow="7095" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
   <si>
     <t>Код</t>
   </si>
@@ -212,9 +212,6 @@
   </si>
   <si>
     <t>Интернет-банк должен отображать персонализированный для каждого клиента список доступных депозитов с актуальными ставками</t>
-  </si>
-  <si>
-    <t>Сайт</t>
   </si>
   <si>
     <t>Интернет-банк: обязательными параметрами для создания заявки на открытие дипозита должны быть номер счета и сумма депозита</t>
@@ -652,7 +649,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr defaultColWidth="10.42578125" defaultRowHeight="12.75"/>
   <cols>
     <col min="2" max="2" width="6.85546875" customWidth="1"/>
@@ -682,312 +679,304 @@
       </c>
       <c r="D4" s="14"/>
     </row>
-    <row r="5" spans="2:4" ht="30" customHeight="1">
-      <c r="B5" s="2"/>
-      <c r="C5" s="13" t="s">
+    <row r="5" spans="2:4" ht="31.5">
+      <c r="B5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" s="3"/>
+    </row>
+    <row r="6" spans="2:4" ht="63">
+      <c r="B6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D6" s="3"/>
+    </row>
+    <row r="7" spans="2:4" ht="94.5">
+      <c r="B7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D7" s="3"/>
+    </row>
+    <row r="8" spans="2:4" ht="47.25">
+      <c r="B8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D8" s="3"/>
+    </row>
+    <row r="9" spans="2:4" ht="78.75">
+      <c r="B9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="D5" s="14"/>
-    </row>
-    <row r="6" spans="2:4" ht="31.5">
-      <c r="B6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="D6" s="3"/>
-    </row>
-    <row r="7" spans="2:4" ht="63">
-      <c r="B7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="D7" s="3"/>
-    </row>
-    <row r="8" spans="2:4" ht="94.5">
-      <c r="B8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="D8" s="3"/>
-    </row>
-    <row r="9" spans="2:4" ht="47.25">
-      <c r="B9" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>62</v>
-      </c>
       <c r="D9" s="3"/>
     </row>
-    <row r="10" spans="2:4" ht="78.75">
+    <row r="10" spans="2:4" ht="63">
       <c r="B10" s="2" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="C10" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" s="3"/>
+    </row>
+    <row r="11" spans="2:4" ht="31.5">
+      <c r="B11" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="D10" s="3"/>
-    </row>
-    <row r="11" spans="2:4" ht="63">
-      <c r="B11" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>69</v>
-      </c>
       <c r="D11" s="3"/>
     </row>
-    <row r="12" spans="2:4" ht="31.5">
+    <row r="12" spans="2:4" ht="47.25">
       <c r="B12" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>66</v>
       </c>
       <c r="D12" s="3"/>
     </row>
-    <row r="13" spans="2:4" ht="47.25">
+    <row r="13" spans="2:4" ht="63">
       <c r="B13" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>67</v>
       </c>
       <c r="D13" s="3"/>
     </row>
-    <row r="14" spans="2:4" ht="63">
+    <row r="14" spans="2:4" ht="30" customHeight="1">
       <c r="B14" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="D14" s="3"/>
-    </row>
-    <row r="15" spans="2:4" ht="30" customHeight="1">
+        <v>5</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="D14" s="14"/>
+    </row>
+    <row r="15" spans="2:4">
       <c r="B15" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="D15" s="14"/>
-    </row>
-    <row r="16" spans="2:4" ht="63">
+        <v>17</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D15" s="3"/>
+    </row>
+    <row r="16" spans="2:4" ht="47.25">
       <c r="B16" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>42</v>
+        <v>18</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>45</v>
       </c>
       <c r="D16" s="3"/>
     </row>
-    <row r="17" spans="1:4" ht="47.25">
+    <row r="17" spans="1:4" ht="30" customHeight="1">
       <c r="B17" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="D17" s="3"/>
-    </row>
-    <row r="18" spans="1:4" ht="30" customHeight="1">
+        <v>7</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="14"/>
+    </row>
+    <row r="18" spans="1:4" ht="47.25">
       <c r="B18" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="D18" s="14"/>
+        <v>19</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D18" s="3"/>
     </row>
     <row r="19" spans="1:4" ht="47.25">
       <c r="B19" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>31</v>
+        <v>20</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>57</v>
       </c>
       <c r="D19" s="3"/>
     </row>
-    <row r="20" spans="1:4" ht="47.25">
+    <row r="20" spans="1:4" ht="31.5">
       <c r="B20" s="2" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="D20" s="3"/>
     </row>
     <row r="21" spans="1:4" ht="31.5">
       <c r="B21" s="2" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="D21" s="3"/>
-    </row>
-    <row r="22" spans="1:4" ht="31.5">
+        <v>50</v>
+      </c>
+      <c r="D21" s="11"/>
+    </row>
+    <row r="22" spans="1:4" ht="63">
       <c r="B22" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D22" s="11"/>
     </row>
-    <row r="23" spans="1:4" ht="63">
+    <row r="23" spans="1:4" ht="30" customHeight="1">
       <c r="B23" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="D23" s="11"/>
-    </row>
-    <row r="24" spans="1:4" ht="30" customHeight="1">
+        <v>9</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" s="14"/>
+    </row>
+    <row r="24" spans="1:4" ht="47.25">
       <c r="B24" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C24" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="D24" s="14"/>
-    </row>
-    <row r="25" spans="1:4" ht="47.25">
+        <v>21</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="D24" s="3"/>
+    </row>
+    <row r="25" spans="1:4" ht="63">
       <c r="B25" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C25" s="10" t="s">
-        <v>44</v>
+        <v>22</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>52</v>
       </c>
       <c r="D25" s="3"/>
     </row>
     <row r="26" spans="1:4" ht="63">
       <c r="B26" s="2" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="D26" s="3"/>
-    </row>
-    <row r="27" spans="1:4" ht="63">
+        <v>53</v>
+      </c>
+      <c r="D26" s="12"/>
+    </row>
+    <row r="27" spans="1:4" ht="30" customHeight="1">
       <c r="B27" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="D27" s="12"/>
+        <v>11</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="D27" s="14"/>
     </row>
     <row r="28" spans="1:4" ht="30" customHeight="1">
       <c r="B28" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="D28" s="14"/>
-    </row>
-    <row r="29" spans="1:4" ht="30" customHeight="1">
+        <v>23</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D28" s="3"/>
+    </row>
+    <row r="29" spans="1:4" ht="47.25">
       <c r="B29" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>48</v>
+        <v>24</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>54</v>
       </c>
       <c r="D29" s="3"/>
     </row>
-    <row r="30" spans="1:4" ht="47.25">
+    <row r="30" spans="1:4" ht="30" customHeight="1">
       <c r="B30" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D30" s="3"/>
-    </row>
-    <row r="31" spans="1:4" ht="30" customHeight="1">
-      <c r="B31" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C31" s="13" t="s">
+      <c r="C30" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="D31" s="14"/>
-    </row>
-    <row r="32" spans="1:4" ht="35.25" customHeight="1">
+      <c r="D30" s="14"/>
+    </row>
+    <row r="31" spans="1:4" ht="35.25" customHeight="1">
+      <c r="A31" s="5"/>
+      <c r="B31" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D31" s="3"/>
+    </row>
+    <row r="32" spans="1:4" ht="63">
       <c r="A32" s="5"/>
       <c r="B32" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D32" s="3"/>
     </row>
-    <row r="33" spans="1:4" ht="63">
-      <c r="A33" s="5"/>
+    <row r="33" spans="2:4" ht="94.5">
       <c r="B33" s="6" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="D33" s="3"/>
     </row>
-    <row r="34" spans="1:4" ht="94.5">
+    <row r="34" spans="2:4" ht="31.5">
       <c r="B34" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D34" s="3"/>
     </row>
-    <row r="35" spans="1:4" ht="31.5">
+    <row r="35" spans="2:4" ht="94.5">
       <c r="B35" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D35" s="3"/>
     </row>
-    <row r="36" spans="1:4" ht="94.5">
+    <row r="36" spans="2:4" ht="63">
       <c r="B36" s="6" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D36" s="3"/>
-    </row>
-    <row r="37" spans="1:4" ht="63">
-      <c r="B37" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C37" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="D37" s="9"/>
+      <c r="D36" s="9"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="C31:D31"/>
+  <mergeCells count="6">
+    <mergeCell ref="C30:D30"/>
     <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C27:D27"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51181102362204689" footer="0.51181102362204689"/>

--- a/Exc2/FURPS_table.xlsx
+++ b/Exc2/FURPS_table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\architecture-sprint-9\Exc2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB862E9B-A5EA-4C0C-8A66-F2AC6C1D6587}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27F79BE1-D384-47F4-BEBC-0DCA641335D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6375" yWindow="7095" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -133,9 +133,6 @@
     <t>+R5</t>
   </si>
   <si>
-    <t>В качестве брокера сообщений должна использоваться Kafka</t>
-  </si>
-  <si>
     <t>Текущие доработки должны сопровождаться архитектурой решения, которая должна содержать в себе документацию всех изменений в полном объеме</t>
   </si>
   <si>
@@ -227,6 +224,9 @@
   </si>
   <si>
     <t>Интернет-банк: клиента должен подтверждать создание заявки на открытие депозита с помощью СМС-кода от банка</t>
+  </si>
+  <si>
+    <t>В качестве брокера сообщений должна использоваться Apache Kafka</t>
   </si>
 </sst>
 </file>
@@ -684,7 +684,7 @@
         <v>15</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D5" s="3"/>
     </row>
@@ -693,7 +693,7 @@
         <v>16</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D6" s="3"/>
     </row>
@@ -702,7 +702,7 @@
         <v>27</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D7" s="3"/>
     </row>
@@ -711,7 +711,7 @@
         <v>28</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D8" s="3"/>
     </row>
@@ -720,43 +720,43 @@
         <v>29</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D9" s="3"/>
     </row>
     <row r="10" spans="2:4" ht="63">
       <c r="B10" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D10" s="3"/>
     </row>
     <row r="11" spans="2:4" ht="31.5">
       <c r="B11" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D11" s="3"/>
     </row>
     <row r="12" spans="2:4" ht="47.25">
       <c r="B12" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D12" s="3"/>
     </row>
     <row r="13" spans="2:4" ht="63">
       <c r="B13" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D13" s="3"/>
     </row>
@@ -774,7 +774,7 @@
         <v>17</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D15" s="3"/>
     </row>
@@ -783,7 +783,7 @@
         <v>18</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D16" s="3"/>
     </row>
@@ -810,7 +810,7 @@
         <v>20</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D19" s="3"/>
     </row>
@@ -819,25 +819,25 @@
         <v>30</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D20" s="3"/>
     </row>
     <row r="21" spans="1:4" ht="31.5">
       <c r="B21" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D21" s="11"/>
     </row>
     <row r="22" spans="1:4" ht="63">
       <c r="B22" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D22" s="11"/>
     </row>
@@ -855,7 +855,7 @@
         <v>21</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D24" s="3"/>
     </row>
@@ -864,16 +864,16 @@
         <v>22</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D25" s="3"/>
     </row>
     <row r="26" spans="1:4" ht="63">
       <c r="B26" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D26" s="12"/>
     </row>
@@ -891,7 +891,7 @@
         <v>23</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D28" s="3"/>
     </row>
@@ -900,7 +900,7 @@
         <v>24</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D29" s="3"/>
     </row>
@@ -938,16 +938,16 @@
         <v>34</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D33" s="3"/>
     </row>
-    <row r="34" spans="2:4" ht="31.5">
+    <row r="34" spans="2:4" ht="47.25">
       <c r="B34" s="6" t="s">
         <v>35</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="D34" s="3"/>
     </row>
@@ -956,16 +956,16 @@
         <v>36</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D35" s="3"/>
     </row>
     <row r="36" spans="2:4" ht="63">
       <c r="B36" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C36" s="7" t="s">
         <v>39</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>40</v>
       </c>
       <c r="D36" s="9"/>
     </row>

--- a/Exc2/FURPS_table.xlsx
+++ b/Exc2/FURPS_table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\architecture-sprint-9\Exc2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27F79BE1-D384-47F4-BEBC-0DCA641335D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6C85D66-04E3-496F-928B-DF1D7E9ED38E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6375" yWindow="7095" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Exc2/FURPS_table.xlsx
+++ b/Exc2/FURPS_table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\architecture-sprint-9\Exc2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6C85D66-04E3-496F-928B-DF1D7E9ED38E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAE45CFB-0F3F-47BF-B110-C96FBD2EF286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6375" yWindow="7095" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="75">
   <si>
     <t>Код</t>
   </si>
@@ -172,6 +172,9 @@
     <t>Сервисы и интернет-банк должны быть доступны 99,9%</t>
   </si>
   <si>
+    <t>R6</t>
+  </si>
+  <si>
     <t>В случае сбоя основного ЦОД работа системы должна переключаться на резервный ЦОД</t>
   </si>
   <si>
@@ -211,6 +214,9 @@
     <t>Интернет-банк должен отображать персонализированный для каждого клиента список доступных депозитов с актуальными ставками</t>
   </si>
   <si>
+    <t>F10</t>
+  </si>
+  <si>
     <t>Интернет-банк: обязательными параметрами для создания заявки на открытие дипозита должны быть номер счета и сумма депозита</t>
   </si>
   <si>
@@ -223,10 +229,22 @@
     <t>АБС: должен отправлять СМС-уведомление клиенту после успешного подтверждения условий открытия депозита</t>
   </si>
   <si>
-    <t>Интернет-банк: клиента должен подтверждать создание заявки на открытие депозита с помощью СМС-кода от банка</t>
-  </si>
-  <si>
     <t>В качестве брокера сообщений должна использоваться Apache Kafka</t>
+  </si>
+  <si>
+    <t>F11</t>
+  </si>
+  <si>
+    <t>СМС-код подтверждения банка должен быть одноразовым для каждого запроса открытия нового депозита</t>
+  </si>
+  <si>
+    <t>После обработки новой заявки на открытие нового депозита клиент должен получить СМС-уведомление о подтверждении или отказе открытии нового депозита</t>
+  </si>
+  <si>
+    <t>Интернет-банк: клиент должен подтверждать создание заявки на открытие депозита с помощью СМС-кода от банка</t>
+  </si>
+  <si>
+    <t>Интернет-банк: после истечения срока ожидания введения СМС-кода от банка, клиент должен повторить оформление заявки с ожиданием нового СМС-кода</t>
   </si>
 </sst>
 </file>
@@ -379,7 +397,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -420,6 +438,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -649,7 +673,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr defaultColWidth="10.42578125" defaultRowHeight="12.75"/>
   <cols>
     <col min="2" max="2" width="6.85546875" customWidth="1"/>
@@ -684,7 +708,7 @@
         <v>15</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D5" s="3"/>
     </row>
@@ -693,7 +717,7 @@
         <v>16</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D6" s="3"/>
     </row>
@@ -702,7 +726,7 @@
         <v>27</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D7" s="3"/>
     </row>
@@ -711,7 +735,7 @@
         <v>28</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D8" s="3"/>
     </row>
@@ -720,7 +744,7 @@
         <v>29</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D9" s="3"/>
     </row>
@@ -729,254 +753,281 @@
         <v>40</v>
       </c>
       <c r="C10" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="D10" s="3"/>
+    </row>
+    <row r="11" spans="2:4" ht="78.75">
+      <c r="B11" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="D11" s="3"/>
+    </row>
+    <row r="12" spans="2:4" ht="31.5">
+      <c r="B12" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D12" s="3"/>
+    </row>
+    <row r="13" spans="2:4" ht="47.25">
+      <c r="B13" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C13" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="D10" s="3"/>
-    </row>
-    <row r="11" spans="2:4" ht="31.5">
-      <c r="B11" s="2" t="s">
+      <c r="D13" s="3"/>
+    </row>
+    <row r="14" spans="2:4" ht="63">
+      <c r="B14" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" s="3"/>
+    </row>
+    <row r="15" spans="2:4" ht="94.5">
+      <c r="B15" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="D15" s="12"/>
+    </row>
+    <row r="16" spans="2:4" ht="30" customHeight="1">
+      <c r="B16" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="D16" s="14"/>
+    </row>
+    <row r="17" spans="2:4">
+      <c r="B17" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D17" s="3"/>
+    </row>
+    <row r="18" spans="2:4" ht="47.25">
+      <c r="B18" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D18" s="3"/>
+    </row>
+    <row r="19" spans="2:4" ht="30" customHeight="1">
+      <c r="B19" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="14"/>
+    </row>
+    <row r="20" spans="2:4" ht="47.25">
+      <c r="B20" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D20" s="3"/>
+    </row>
+    <row r="21" spans="2:4" ht="47.25">
+      <c r="B21" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D21" s="3"/>
+    </row>
+    <row r="22" spans="2:4" ht="31.5">
+      <c r="B22" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D22" s="3"/>
+    </row>
+    <row r="23" spans="2:4" ht="31.5">
+      <c r="B23" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D23" s="11"/>
+    </row>
+    <row r="24" spans="2:4" ht="63">
+      <c r="B24" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D24" s="11"/>
+    </row>
+    <row r="25" spans="2:4" ht="63">
+      <c r="B25" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="D25" s="16"/>
+    </row>
+    <row r="26" spans="2:4" ht="30" customHeight="1">
+      <c r="B26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26" s="14"/>
+    </row>
+    <row r="27" spans="2:4" ht="47.25">
+      <c r="B27" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D27" s="3"/>
+    </row>
+    <row r="28" spans="2:4" ht="63">
+      <c r="B28" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D28" s="3"/>
+    </row>
+    <row r="29" spans="2:4" ht="63">
+      <c r="B29" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="D11" s="3"/>
-    </row>
-    <row r="12" spans="2:4" ht="47.25">
-      <c r="B12" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="D12" s="3"/>
-    </row>
-    <row r="13" spans="2:4" ht="63">
-      <c r="B13" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="D13" s="3"/>
-    </row>
-    <row r="14" spans="2:4" ht="30" customHeight="1">
-      <c r="B14" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="D14" s="14"/>
-    </row>
-    <row r="15" spans="2:4">
-      <c r="B15" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="D15" s="3"/>
-    </row>
-    <row r="16" spans="2:4" ht="47.25">
-      <c r="B16" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="D16" s="3"/>
-    </row>
-    <row r="17" spans="1:4" ht="30" customHeight="1">
-      <c r="B17" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="D17" s="14"/>
-    </row>
-    <row r="18" spans="1:4" ht="47.25">
-      <c r="B18" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D18" s="3"/>
-    </row>
-    <row r="19" spans="1:4" ht="47.25">
-      <c r="B19" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="D19" s="3"/>
-    </row>
-    <row r="20" spans="1:4" ht="31.5">
-      <c r="B20" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="D20" s="3"/>
-    </row>
-    <row r="21" spans="1:4" ht="31.5">
-      <c r="B21" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="D21" s="11"/>
-    </row>
-    <row r="22" spans="1:4" ht="63">
-      <c r="B22" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="D22" s="11"/>
-    </row>
-    <row r="23" spans="1:4" ht="30" customHeight="1">
-      <c r="B23" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C23" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="D23" s="14"/>
-    </row>
-    <row r="24" spans="1:4" ht="47.25">
-      <c r="B24" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C24" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="D24" s="3"/>
-    </row>
-    <row r="25" spans="1:4" ht="63">
-      <c r="B25" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="D25" s="3"/>
-    </row>
-    <row r="26" spans="1:4" ht="63">
-      <c r="B26" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="D26" s="12"/>
-    </row>
-    <row r="27" spans="1:4" ht="30" customHeight="1">
-      <c r="B27" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="D27" s="14"/>
-    </row>
-    <row r="28" spans="1:4" ht="30" customHeight="1">
-      <c r="B28" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D28" s="3"/>
-    </row>
-    <row r="29" spans="1:4" ht="47.25">
-      <c r="B29" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="D29" s="3"/>
-    </row>
-    <row r="30" spans="1:4" ht="30" customHeight="1">
+      <c r="D29" s="12"/>
+    </row>
+    <row r="30" spans="2:4" ht="30" customHeight="1">
       <c r="B30" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="D30" s="14"/>
+    </row>
+    <row r="31" spans="2:4" ht="30" customHeight="1">
+      <c r="B31" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D31" s="3"/>
+    </row>
+    <row r="32" spans="2:4" ht="47.25">
+      <c r="B32" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D32" s="3"/>
+    </row>
+    <row r="33" spans="1:4" ht="30" customHeight="1">
+      <c r="B33" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="13" t="s">
+      <c r="C33" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="D30" s="14"/>
-    </row>
-    <row r="31" spans="1:4" ht="35.25" customHeight="1">
-      <c r="A31" s="5"/>
-      <c r="B31" s="6" t="s">
+      <c r="D33" s="14"/>
+    </row>
+    <row r="34" spans="1:4" ht="35.25" customHeight="1">
+      <c r="A34" s="5"/>
+      <c r="B34" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="C34" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="D31" s="3"/>
-    </row>
-    <row r="32" spans="1:4" ht="63">
-      <c r="A32" s="5"/>
-      <c r="B32" s="6" t="s">
+      <c r="D34" s="3"/>
+    </row>
+    <row r="35" spans="1:4" ht="63">
+      <c r="A35" s="5"/>
+      <c r="B35" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="C35" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D32" s="3"/>
-    </row>
-    <row r="33" spans="2:4" ht="94.5">
-      <c r="B33" s="6" t="s">
+      <c r="D35" s="3"/>
+    </row>
+    <row r="36" spans="1:4" ht="94.5">
+      <c r="B36" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="C36" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D33" s="3"/>
-    </row>
-    <row r="34" spans="2:4" ht="47.25">
-      <c r="B34" s="6" t="s">
+      <c r="D36" s="3"/>
+    </row>
+    <row r="37" spans="1:4" ht="47.25">
+      <c r="B37" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C34" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="D34" s="3"/>
-    </row>
-    <row r="35" spans="2:4" ht="94.5">
-      <c r="B35" s="6" t="s">
+      <c r="C37" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D37" s="3"/>
+    </row>
+    <row r="38" spans="1:4" ht="94.5">
+      <c r="B38" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C35" s="7" t="s">
+      <c r="C38" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D35" s="3"/>
-    </row>
-    <row r="36" spans="2:4" ht="63">
-      <c r="B36" s="6" t="s">
+      <c r="D38" s="3"/>
+    </row>
+    <row r="39" spans="1:4" ht="63">
+      <c r="B39" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C36" s="7" t="s">
+      <c r="C39" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D36" s="9"/>
+      <c r="D39" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C26:D26"/>
     <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C27:D27"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51181102362204689" footer="0.51181102362204689"/>
